--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pge-my.sharepoint.com/personal/sih5_pge_com/Documents/Desktop/transformer failures/txfr_brkr_failures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="8_{B2A53C57-5DB4-497C-994E-77DB12CCF767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD99FF63-7B0D-4E2A-876E-E8F573445A65}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="8_{B2A53C57-5DB4-497C-994E-77DB12CCF767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2514C40E-70DE-497B-A51C-9B787C7B7931}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-390" windowWidth="29040" windowHeight="17520" xr2:uid="{E5020393-C745-4F5D-8817-A166F6886FC2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E5020393-C745-4F5D-8817-A166F6886FC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -152,16 +152,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -508,292 +508,312 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
       <c r="F2" s="1"/>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="2"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4">
+      <c r="K3" s="5"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2">
         <v>2025</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="2">
         <v>2026</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="2"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>3734</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>3014</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="4" t="s">
+      <c r="K4" s="5"/>
+      <c r="L4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="2">
         <v>102</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="2">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>456</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>1923</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="4" t="s">
+      <c r="K5" s="5"/>
+      <c r="L5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="2">
         <v>84</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
       <c r="F6" s="1"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
       <c r="F7" s="1"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="3" t="s">
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4" t="s">
+      <c r="K9" s="5"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="4" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2">
         <v>3734</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="2">
         <v>3014</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>1</v>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="4" t="s">
+      <c r="K10" s="5"/>
+      <c r="L10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="N10" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="4" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="2">
         <v>456</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="2">
         <v>1923</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>6</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="4" t="s">
+      <c r="K11" s="5"/>
+      <c r="L11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C18" s="4"/>
-      <c r="D18" s="4">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2">
         <v>1</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="2">
         <v>2</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>3</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="2">
         <v>4</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C19" s="4" t="s">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="2">
         <v>251</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="2">
         <v>127</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>41</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="2">
         <v>34</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C20" s="4" t="s">
+      <c r="J19">
+        <f>SUM(D19:D20)</f>
+        <v>973</v>
+      </c>
+      <c r="K19">
+        <f t="shared" ref="K19:L19" si="0">SUM(E19:E20)</f>
+        <v>726</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="0"/>
+        <v>393</v>
+      </c>
+      <c r="M19">
+        <f>SUM(G19:G20)</f>
+        <v>252</v>
+      </c>
+      <c r="N19">
+        <f t="shared" ref="N19" si="1">SUM(H19:H20)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="2">
         <v>722</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="2">
         <v>599</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>352</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="2">
         <v>218</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C21" s="4" t="s">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="2">
         <v>570</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="2">
         <v>1412</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>1159</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="2">
         <v>589</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C22" s="4" t="s">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="2">
         <v>225</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="2">
         <v>1070</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>460</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="2">
         <v>1059</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="2">
         <v>200</v>
       </c>
     </row>
